--- a/data/trans_bre/P16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,23</t>
+          <t>-3,91; 1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,88</t>
+          <t>-1,82; 4,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,32</t>
+          <t>-1,94; 4,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,71</t>
+          <t>-0,54; 5,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,4; 55,75</t>
+          <t>-74,95; 54,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 163,68</t>
+          <t>-35,64; 181,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 203,92</t>
+          <t>-40,39; 165,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 242,03</t>
+          <t>-22,2; 262,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,54</t>
+          <t>3,57; 9,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,68</t>
+          <t>-1,16; 6,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,02</t>
+          <t>-1,56; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,2</t>
+          <t>1,41; 7,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>195,67; —</t>
+          <t>169,74; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 194,53</t>
+          <t>-21,86; 212,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 209,19</t>
+          <t>-32,42; 192,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 316,04</t>
+          <t>24,43; 369,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,99</t>
+          <t>-2,96; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,22</t>
+          <t>-1,19; 5,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,21</t>
+          <t>1,92; 11,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,93</t>
+          <t>-0,23; 7,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 104,34</t>
+          <t>-85,87; 133,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 226,84</t>
+          <t>-29,09; 240,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,93; 716,02</t>
+          <t>44,13; 737,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 584,74</t>
+          <t>-8,52; 603,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,56</t>
+          <t>0,21; 3,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,15</t>
+          <t>2,82; 7,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,56</t>
+          <t>1,82; 5,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,55</t>
+          <t>-1,66; 2,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 203,51</t>
+          <t>3,22; 207,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,09; 400,79</t>
+          <t>86,37; 407,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,52; 311,5</t>
+          <t>56,13; 310,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 110,63</t>
+          <t>-43,55; 115,12</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,81</t>
+          <t>-0,36; 3,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,15</t>
+          <t>-0,96; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,09</t>
+          <t>-0,31; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 32,1</t>
+          <t>-1,08; 30,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 509,05</t>
+          <t>-25,78; 462,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 171,22</t>
+          <t>-27,32; 184,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 174,01</t>
+          <t>-9,78; 170,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 1353,05</t>
+          <t>-25,93; 1091,4</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,22</t>
+          <t>-1,01; 2,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,72</t>
+          <t>-4,82; 1,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,36</t>
+          <t>-3,34; 2,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,54</t>
+          <t>-7,91; 2,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 267,09</t>
+          <t>-24,79; 254,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 50,79</t>
+          <t>-53,33; 49,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 71,84</t>
+          <t>-45,03; 89,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,03; 183,5</t>
+          <t>-75,75; 194,56</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,36</t>
+          <t>0,72; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,11</t>
+          <t>1,03; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,29</t>
+          <t>1,35; 3,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,57</t>
+          <t>0,84; 9,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,32; 112,85</t>
+          <t>24,64; 122,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,49; 105,39</t>
+          <t>25,83; 104,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,13; 121,98</t>
+          <t>36,98; 123,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,53; 325,2</t>
+          <t>23,84; 334,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,16</t>
+          <t>-4,17; 1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,89</t>
+          <t>-1,56; 4,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,25</t>
+          <t>-1,77; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,19</t>
+          <t>-0,69; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 54,67</t>
+          <t>-76,28; 50,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 181,59</t>
+          <t>-34,27; 146,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 165,56</t>
+          <t>-38,6; 177,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 262,89</t>
+          <t>-20,4; 260,07</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124,2%</t>
+          <t>125,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,7</t>
+          <t>3,74; 9,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,11</t>
+          <t>-1,25; 6,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,69</t>
+          <t>-1,34; 4,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,51</t>
+          <t>1,3; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>169,74; —</t>
+          <t>159,11; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 212,29</t>
+          <t>-23,6; 189,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 192,99</t>
+          <t>-29,61; 224,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 369,57</t>
+          <t>22,93; 325,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,0</t>
+          <t>-2,93; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,47</t>
+          <t>-0,69; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,36</t>
+          <t>1,71; 11,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 7,02</t>
+          <t>-1,93; 4,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 133,0</t>
+          <t>-84,46; 151,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 240,88</t>
+          <t>-23,04; 256,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,13; 737,62</t>
+          <t>33,1; 625,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 603,49</t>
+          <t>-35,74; 140,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,66</t>
+          <t>0,18; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,32</t>
+          <t>2,73; 7,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,67</t>
+          <t>1,92; 5,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,66</t>
+          <t>-0,1; 3,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 207,16</t>
+          <t>2,75; 199,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,37; 407,74</t>
+          <t>76,3; 410,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,13; 310,63</t>
+          <t>54,73; 313,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 115,12</t>
+          <t>-3,66; 132,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>197,47%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,71</t>
+          <t>-0,15; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,32</t>
+          <t>-1,06; 3,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,12</t>
+          <t>-0,24; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 30,22</t>
+          <t>-1,21; 3,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 462,29</t>
+          <t>-15,08; 520,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 184,76</t>
+          <t>-29,17; 167,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 170,41</t>
+          <t>-9,18; 165,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 1091,4</t>
+          <t>-23,07; 146,62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,96%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,94</t>
+          <t>-0,84; 2,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,7</t>
+          <t>-4,69; 1,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,55</t>
+          <t>-3,2; 2,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,51</t>
+          <t>-4,54; 3,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 254,92</t>
+          <t>-21,54; 270,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 49,6</t>
+          <t>-53,64; 49,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 89,91</t>
+          <t>-44,34; 90,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 194,56</t>
+          <t>-62,92; 234,47</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,43</t>
+          <t>0,68; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,08</t>
+          <t>0,99; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,34</t>
+          <t>1,36; 3,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,97</t>
+          <t>0,65; 2,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,64; 122,29</t>
+          <t>23,87; 118,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 104,1</t>
+          <t>24,83; 108,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,98; 123,87</t>
+          <t>38,49; 124,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,84; 334,0</t>
+          <t>15,36; 91,62</t>
         </is>
       </c>
     </row>
